--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4305555555555556</v>
+        <v>0.4942528735632184</v>
       </c>
       <c r="B2">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.4718309859154929</v>
       </c>
       <c r="D2">
-        <v>0.6826923076923077</v>
+        <v>0.635593220338983</v>
       </c>
       <c r="E2">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4942528735632184</v>
+        <v>0.5058823529411764</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -432,10 +432,10 @@
         <v>0.635593220338983</v>
       </c>
       <c r="E2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2">
         <v>24</v>
